--- a/api/desempenho/2025-07-04.xlsx
+++ b/api/desempenho/2025-07-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,6 +728,146 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:31:03</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>39673</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Usuário acessou a rota Mentorship Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:31:29</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>39750</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Usuário acessou a rota Mentorship Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:32:10</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>39826</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>81.02</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Usuário acessou a rota Mentorship Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:32:50</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>39894</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Usuário acessou a rota Users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:33:16</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>39953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>81.14</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Usuário acessou a rota Mentorship Profiles</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/api/desempenho/2025-07-04.xlsx
+++ b/api/desempenho/2025-07-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:23:36</t>
+          <t>18:14:11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15079</v>
+        <v>21041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -468,403 +468,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80.36</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>11:40:23</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>16445</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>80.41</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>11:40:25</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>16445</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>83.93000000000001</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>13:05:07</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>28428</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13:05:36</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>28428</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>13:06:07</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>28558</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>80.88</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>13:06:09</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>28558</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13:06:22</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>28585</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>80.83</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>13:06:41</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>28649</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>80.61</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13:06:43</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>28649</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>84.13</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Acesso na rota UserTechStacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14:31:03</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>39673</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>80.83</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>14:31:29</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>39750</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>80.98999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>14:32:10</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>39826</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>14:32:50</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>39894</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>81.05</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>14:33:16</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>39953</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>81.14</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Usuário acessou a rota Mentorship Profiles</t>
+          <t>Acessou a rota Mentorship Profiles</t>
         </is>
       </c>
     </row>

--- a/api/desempenho/2025-07-04.xlsx
+++ b/api/desempenho/2025-07-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,62 @@
         <v>80.31999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Acessou a rota Mentorship Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>18:30:14</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23809</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Acesso na rota UserTechStacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>18:33:42</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24340</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Acessou a rota Mentorship Profiles</t>
         </is>
